--- a/artfynd/A 12958-2026 artfynd.xlsx
+++ b/artfynd/A 12958-2026 artfynd.xlsx
@@ -924,7 +924,7 @@
         <v>131672498</v>
       </c>
       <c r="B4" t="n">
-        <v>92251</v>
+        <v>92252</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1176,7 +1176,7 @@
         <v>131672467</v>
       </c>
       <c r="B6" t="n">
-        <v>92246</v>
+        <v>92247</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 12958-2026 artfynd.xlsx
+++ b/artfynd/A 12958-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131671841</v>
       </c>
       <c r="B2" t="n">
-        <v>91828</v>
+        <v>91829</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -806,7 +806,7 @@
         <v>131672031</v>
       </c>
       <c r="B3" t="n">
-        <v>5197</v>
+        <v>5198</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -921,10 +921,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131672498</v>
+        <v>131673113</v>
       </c>
       <c r="B4" t="n">
-        <v>92252</v>
+        <v>57087</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -932,52 +932,49 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4217</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Rimbo, tallåga, Upl</t>
+          <t>Riddarbolsmossen, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>674838</v>
+        <v>674871</v>
       </c>
       <c r="R4" t="n">
-        <v>6633019</v>
+        <v>6632981</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1006,7 +1003,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1016,7 +1013,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:52</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>50 tuppkrokar under mattall</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1025,14 +1027,8 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Tallåga</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1049,10 +1045,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131673113</v>
+        <v>131672498</v>
       </c>
       <c r="B5" t="n">
-        <v>57086</v>
+        <v>92253</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1060,49 +1056,52 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>4217</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Riddarbolsmossen, Upl</t>
+          <t>Rimbo, tallåga, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>674871</v>
+        <v>674838</v>
       </c>
       <c r="R5" t="n">
-        <v>6632981</v>
+        <v>6633019</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1131,7 +1130,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1141,12 +1140,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:52</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>50 tuppkrokar under mattall</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1155,8 +1149,14 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Tallåga</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1176,7 +1176,7 @@
         <v>131672467</v>
       </c>
       <c r="B6" t="n">
-        <v>92247</v>
+        <v>92248</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 12958-2026 artfynd.xlsx
+++ b/artfynd/A 12958-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131671841</v>
       </c>
       <c r="B2" t="n">
-        <v>91829</v>
+        <v>91832</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -921,10 +921,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131673113</v>
+        <v>131672498</v>
       </c>
       <c r="B4" t="n">
-        <v>57087</v>
+        <v>92256</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -932,49 +932,52 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>4217</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Riddarbolsmossen, Upl</t>
+          <t>Rimbo, tallåga, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>674871</v>
+        <v>674838</v>
       </c>
       <c r="R4" t="n">
-        <v>6632981</v>
+        <v>6633019</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1003,7 +1006,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1013,12 +1016,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:52</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>50 tuppkrokar under mattall</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1027,8 +1025,14 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Tallåga</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1045,10 +1049,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131672498</v>
+        <v>131673113</v>
       </c>
       <c r="B5" t="n">
-        <v>92253</v>
+        <v>57090</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1056,52 +1060,49 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4217</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Rimbo, tallåga, Upl</t>
+          <t>Riddarbolsmossen, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>674838</v>
+        <v>674871</v>
       </c>
       <c r="R5" t="n">
-        <v>6633019</v>
+        <v>6632981</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1130,7 +1131,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1140,7 +1141,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:52</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>50 tuppkrokar under mattall</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1149,14 +1155,8 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Tallåga</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1176,7 +1176,7 @@
         <v>131672467</v>
       </c>
       <c r="B6" t="n">
-        <v>92248</v>
+        <v>92251</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 12958-2026 artfynd.xlsx
+++ b/artfynd/A 12958-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131671841</v>
       </c>
       <c r="B2" t="n">
-        <v>91832</v>
+        <v>91838</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -924,7 +924,7 @@
         <v>131672498</v>
       </c>
       <c r="B4" t="n">
-        <v>92256</v>
+        <v>92262</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1052,7 +1052,7 @@
         <v>131673113</v>
       </c>
       <c r="B5" t="n">
-        <v>57090</v>
+        <v>57092</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1176,7 +1176,7 @@
         <v>131672467</v>
       </c>
       <c r="B6" t="n">
-        <v>92251</v>
+        <v>92257</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 12958-2026 artfynd.xlsx
+++ b/artfynd/A 12958-2026 artfynd.xlsx
@@ -921,10 +921,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131672498</v>
+        <v>131673113</v>
       </c>
       <c r="B4" t="n">
-        <v>92262</v>
+        <v>57092</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -932,52 +932,49 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4217</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Rimbo, tallåga, Upl</t>
+          <t>Riddarbolsmossen, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>674838</v>
+        <v>674871</v>
       </c>
       <c r="R4" t="n">
-        <v>6633019</v>
+        <v>6632981</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1006,7 +1003,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1016,7 +1013,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:52</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>50 tuppkrokar under mattall</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1025,14 +1027,8 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Tallåga</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1049,10 +1045,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131673113</v>
+        <v>131672498</v>
       </c>
       <c r="B5" t="n">
-        <v>57092</v>
+        <v>92262</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1060,49 +1056,52 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>4217</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Riddarbolsmossen, Upl</t>
+          <t>Rimbo, tallåga, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>674871</v>
+        <v>674838</v>
       </c>
       <c r="R5" t="n">
-        <v>6632981</v>
+        <v>6633019</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1131,7 +1130,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1141,12 +1140,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:52</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>50 tuppkrokar under mattall</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1155,8 +1149,14 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Tallåga</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">

--- a/artfynd/A 12958-2026 artfynd.xlsx
+++ b/artfynd/A 12958-2026 artfynd.xlsx
@@ -921,10 +921,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131673113</v>
+        <v>131672498</v>
       </c>
       <c r="B4" t="n">
-        <v>57092</v>
+        <v>92262</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -932,49 +932,52 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>4217</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Riddarbolsmossen, Upl</t>
+          <t>Rimbo, tallåga, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>674871</v>
+        <v>674838</v>
       </c>
       <c r="R4" t="n">
-        <v>6632981</v>
+        <v>6633019</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1003,7 +1006,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1013,12 +1016,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:52</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>50 tuppkrokar under mattall</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1027,8 +1025,14 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Tallåga</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1045,10 +1049,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131672498</v>
+        <v>131673113</v>
       </c>
       <c r="B5" t="n">
-        <v>92262</v>
+        <v>57092</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1056,52 +1060,49 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4217</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Rimbo, tallåga, Upl</t>
+          <t>Riddarbolsmossen, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>674838</v>
+        <v>674871</v>
       </c>
       <c r="R5" t="n">
-        <v>6633019</v>
+        <v>6632981</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1130,7 +1131,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1140,7 +1141,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:52</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>50 tuppkrokar under mattall</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1149,14 +1155,8 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Tallåga</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">

--- a/artfynd/A 12958-2026 artfynd.xlsx
+++ b/artfynd/A 12958-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131671841</v>
       </c>
       <c r="B2" t="n">
-        <v>91838</v>
+        <v>91841</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -806,7 +806,7 @@
         <v>131672031</v>
       </c>
       <c r="B3" t="n">
-        <v>5198</v>
+        <v>5199</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -921,10 +921,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131673113</v>
+        <v>131672498</v>
       </c>
       <c r="B4" t="n">
-        <v>57092</v>
+        <v>92265</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -932,49 +932,52 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>4217</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Riddarbolsmossen, Upl</t>
+          <t>Rimbo, tallåga, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>674871</v>
+        <v>674838</v>
       </c>
       <c r="R4" t="n">
-        <v>6632981</v>
+        <v>6633019</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1003,7 +1006,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1013,12 +1016,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:52</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>50 tuppkrokar under mattall</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1027,8 +1025,14 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Tallåga</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1045,10 +1049,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131672498</v>
+        <v>131673113</v>
       </c>
       <c r="B5" t="n">
-        <v>92262</v>
+        <v>57095</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1056,52 +1060,49 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4217</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Rimbo, tallåga, Upl</t>
+          <t>Riddarbolsmossen, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>674838</v>
+        <v>674871</v>
       </c>
       <c r="R5" t="n">
-        <v>6633019</v>
+        <v>6632981</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1130,7 +1131,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1140,7 +1141,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:52</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>50 tuppkrokar under mattall</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1149,14 +1155,8 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Tallåga</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1176,7 +1176,7 @@
         <v>131672467</v>
       </c>
       <c r="B6" t="n">
-        <v>92257</v>
+        <v>92260</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 12958-2026 artfynd.xlsx
+++ b/artfynd/A 12958-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131671841</v>
       </c>
       <c r="B2" t="n">
-        <v>91841</v>
+        <v>91846</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -924,7 +924,7 @@
         <v>131672498</v>
       </c>
       <c r="B4" t="n">
-        <v>92265</v>
+        <v>92270</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1052,7 +1052,7 @@
         <v>131673113</v>
       </c>
       <c r="B5" t="n">
-        <v>57095</v>
+        <v>57100</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1176,7 +1176,7 @@
         <v>131672467</v>
       </c>
       <c r="B6" t="n">
-        <v>92260</v>
+        <v>92265</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 12958-2026 artfynd.xlsx
+++ b/artfynd/A 12958-2026 artfynd.xlsx
@@ -921,10 +921,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131672498</v>
+        <v>131673113</v>
       </c>
       <c r="B4" t="n">
-        <v>92270</v>
+        <v>57100</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -932,52 +932,49 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4217</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Rimbo, tallåga, Upl</t>
+          <t>Riddarbolsmossen, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>674838</v>
+        <v>674871</v>
       </c>
       <c r="R4" t="n">
-        <v>6633019</v>
+        <v>6632981</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1006,7 +1003,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1016,7 +1013,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:52</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>50 tuppkrokar under mattall</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1025,14 +1027,8 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Tallåga</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1049,10 +1045,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131673113</v>
+        <v>131672498</v>
       </c>
       <c r="B5" t="n">
-        <v>57100</v>
+        <v>92270</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1060,49 +1056,52 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>4217</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Riddarbolsmossen, Upl</t>
+          <t>Rimbo, tallåga, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>674871</v>
+        <v>674838</v>
       </c>
       <c r="R5" t="n">
-        <v>6632981</v>
+        <v>6633019</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1131,7 +1130,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1141,12 +1140,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:52</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>50 tuppkrokar under mattall</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1155,8 +1149,14 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Tallåga</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">

--- a/artfynd/A 12958-2026 artfynd.xlsx
+++ b/artfynd/A 12958-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131671841</v>
       </c>
       <c r="B2" t="n">
-        <v>91889</v>
+        <v>91974</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -803,10 +803,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131672031</v>
+        <v>131672498</v>
       </c>
       <c r="B3" t="n">
-        <v>5199</v>
+        <v>92370</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -814,42 +814,52 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>105930</v>
+        <v>4217</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
+          <t>(Pers.:Fr.) Bondartsev</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Rimbo, granlåga, Upl</t>
+          <t>Rimbo, tallåga, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>674853</v>
+        <v>674838</v>
       </c>
       <c r="R3" t="n">
-        <v>6633016</v>
+        <v>6633019</v>
       </c>
       <c r="S3" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -878,7 +888,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -888,12 +898,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:30</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Spår av vågbandad barkbock i granlåga.</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -905,6 +910,11 @@
       <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Tallåga</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -921,10 +931,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131672498</v>
+        <v>131673113</v>
       </c>
       <c r="B4" t="n">
-        <v>92313</v>
+        <v>57162</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -932,52 +942,49 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4217</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Rimbo, tallåga, Upl</t>
+          <t>Riddarbolsmossen, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>674838</v>
+        <v>674871</v>
       </c>
       <c r="R4" t="n">
-        <v>6633019</v>
+        <v>6632981</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1006,7 +1013,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1016,7 +1023,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:52</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>50 tuppkrokar under mattall</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1025,14 +1037,8 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Tallåga</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1049,10 +1055,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131673113</v>
+        <v>131672031</v>
       </c>
       <c r="B5" t="n">
-        <v>57136</v>
+        <v>5201</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1060,49 +1066,42 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>105930</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Riddarbolsmossen, Upl</t>
+          <t>Rimbo, granlåga, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>674871</v>
+        <v>674853</v>
       </c>
       <c r="R5" t="n">
-        <v>6632981</v>
+        <v>6633016</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1131,7 +1130,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1141,12 +1140,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>50 tuppkrokar under mattall</t>
+          <t>Spår av vågbandad barkbock i granlåga.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1155,6 +1154,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1176,7 +1176,7 @@
         <v>131672467</v>
       </c>
       <c r="B6" t="n">
-        <v>92308</v>
+        <v>92365</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 12958-2026 artfynd.xlsx
+++ b/artfynd/A 12958-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -800,6 +805,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131671841</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -928,6 +938,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131672498</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1052,6 +1067,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131673113</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1170,6 +1190,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131672031</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1298,8 +1323,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131672467</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>